--- a/web/SecureMe_Test_Execution_Report.xlsx
+++ b/web/SecureMe_Test_Execution_Report.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Selenium E2E Testing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="API Integration Testing" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Load &amp; Performance Testing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Vulnerability Assessment" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selenium E2E Testing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Integration Testing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load &amp; Performance Testing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerability Assessment" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 13:59:08 UTC</t>
+          <t>2026-09-03 13:58:18 UTC</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="H2" s="6" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="H4" s="6" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" s="6" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="H36" s="6" t="n">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>170</v>
+        <v>57</v>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="H42" s="6" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>152</v>
+        <v>44</v>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="H44" s="6" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="H46" s="6" t="n">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="H56" s="6" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="H58" s="6" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="H62" s="6" t="n">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="H66" s="6" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="H68" s="6" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="H70" s="6" t="n">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="H74" s="6" t="n">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="H82" s="6" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="H84" s="6" t="n">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="H86" s="6" t="n">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="H88" s="6" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="H92" s="6" t="n">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="H94" s="6" t="n">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="H96" s="6" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="H98" s="6" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="H100" s="6" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="H102" s="6" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="H104" s="6" t="n">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="H106" s="6" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="H108" s="6" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="H109" s="6" t="n">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="H110" s="6" t="n">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="H111" s="6" t="n">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="H112" s="6" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="H113" s="6" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="H114" s="6" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="H115" s="6" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="H116" s="6" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="H117" s="6" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="H118" s="6" t="n">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="H119" s="6" t="n">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="H120" s="6" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="H121" s="6" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="H122" s="6" t="n">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="H123" s="6" t="n">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="H124" s="6" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="H125" s="6" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="H126" s="6" t="n">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="H127" s="6" t="n">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="H128" s="6" t="n">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="H129" s="6" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="H130" s="6" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="H131" s="6" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="H132" s="6" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="H133" s="6" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="H134" s="6" t="n">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="H135" s="6" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="H136" s="6" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="H137" s="6" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="H138" s="6" t="n">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="H139" s="6" t="n">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="H140" s="6" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="H141" s="6" t="n">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="H142" s="6" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="H143" s="6" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="H144" s="6" t="n">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="H145" s="6" t="n">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="H146" s="6" t="n">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="H147" s="6" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="H148" s="6" t="n">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="H149" s="6" t="n">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="H150" s="6" t="n">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="H151" s="6" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="H152" s="6" t="n">
-        <v>37</v>
+        <v>174</v>
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="H153" s="6" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="H154" s="6" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="H155" s="6" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="H156" s="6" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="H157" s="6" t="n">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="H158" s="6" t="n">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="H159" s="6" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="H160" s="6" t="n">
-        <v>155</v>
+        <v>42</v>
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="H161" s="6" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="H162" s="6" t="n">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="H163" s="6" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="H164" s="6" t="n">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="H165" s="6" t="n">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="H166" s="6" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="H167" s="6" t="n">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="H168" s="6" t="n">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="H169" s="6" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="I169" s="8" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="H170" s="6" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="H171" s="6" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="I171" s="8" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="H172" s="6" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="H173" s="6" t="n">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="I173" s="8" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="H174" s="6" t="n">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="H175" s="6" t="n">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="I175" s="8" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         </is>
       </c>
       <c r="H176" s="6" t="n">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="H177" s="6" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="H178" s="6" t="n">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="H179" s="6" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I179" s="8" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="H180" s="6" t="n">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H181" s="6" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="I181" s="8" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="H182" s="6" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="H183" s="6" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="I183" s="8" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="H184" s="6" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="H185" s="6" t="n">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="I185" s="8" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="H186" s="6" t="n">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="I186" s="8" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="H187" s="6" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="I187" s="8" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="H188" s="6" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="H189" s="6" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="I189" s="8" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="H190" s="6" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="I190" s="8" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="H191" s="6" t="n">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="I191" s="8" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="H192" s="6" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="I192" s="8" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="H193" s="6" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I193" s="8" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="H194" s="6" t="n">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="I194" s="8" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="H195" s="6" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="I195" s="8" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="H196" s="6" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I196" s="8" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         </is>
       </c>
       <c r="H197" s="6" t="n">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="I197" s="8" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="H198" s="6" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="I198" s="8" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="H199" s="6" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I199" s="8" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="H200" s="6" t="n">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="I200" s="8" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="H201" s="6" t="n">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="I201" s="8" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="H202" s="6" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="I202" s="8" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="H203" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I203" s="8" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="H204" s="6" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I204" s="8" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="H205" s="6" t="n">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="I205" s="8" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="H206" s="6" t="n">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="I206" s="8" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="H207" s="6" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="I207" s="8" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         </is>
       </c>
       <c r="H208" s="6" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I208" s="8" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="H209" s="6" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="I209" s="8" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="H210" s="6" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="I210" s="8" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         </is>
       </c>
       <c r="H211" s="6" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="I211" s="8" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="H212" s="6" t="n">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="I212" s="8" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="H213" s="6" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I213" s="8" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="H214" s="6" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I214" s="8" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         </is>
       </c>
       <c r="H215" s="6" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="I215" s="8" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         </is>
       </c>
       <c r="H216" s="6" t="n">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="I216" s="8" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="H217" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I217" s="8" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="H218" s="6" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="I218" s="8" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="H219" s="6" t="n">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="I219" s="8" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="H220" s="6" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="I220" s="8" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="H221" s="6" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="I221" s="8" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         </is>
       </c>
       <c r="H222" s="6" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I222" s="8" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         </is>
       </c>
       <c r="H223" s="6" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I223" s="8" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="H224" s="6" t="n">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="I224" s="8" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="H225" s="6" t="n">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="I225" s="8" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="H226" s="6" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         </is>
       </c>
       <c r="H227" s="6" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I227" s="8" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="H228" s="6" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="I228" s="8" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         </is>
       </c>
       <c r="H229" s="6" t="n">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="I229" s="8" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="H230" s="6" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I230" s="8" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         </is>
       </c>
       <c r="H231" s="6" t="n">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="I231" s="8" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="H232" s="6" t="n">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="I232" s="8" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="H233" s="6" t="n">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="I233" s="8" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="H234" s="6" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I234" s="8" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="H235" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I235" s="8" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="H236" s="6" t="n">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="I236" s="8" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         </is>
       </c>
       <c r="H237" s="6" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="I237" s="8" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="H238" s="6" t="n">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="I238" s="8" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="H239" s="6" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="I239" s="8" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="H240" s="6" t="n">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="I240" s="8" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="H241" s="6" t="n">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="I241" s="8" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="H242" s="6" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="I242" s="8" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="H244" s="6" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="I244" s="8" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="H245" s="6" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="I245" s="8" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="H246" s="6" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="I246" s="8" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="H247" s="6" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="I247" s="8" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="H248" s="6" t="n">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="I248" s="8" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         </is>
       </c>
       <c r="H249" s="6" t="n">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="I249" s="8" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="H250" s="6" t="n">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="I250" s="8" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="H251" s="6" t="n">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="I251" s="8" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         </is>
       </c>
       <c r="H252" s="6" t="n">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="I252" s="8" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="H253" s="6" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I253" s="8" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         </is>
       </c>
       <c r="H254" s="6" t="n">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="I254" s="8" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         </is>
       </c>
       <c r="H255" s="6" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I255" s="8" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         </is>
       </c>
       <c r="H256" s="6" t="n">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="I256" s="8" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         </is>
       </c>
       <c r="H257" s="6" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="I257" s="8" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="H258" s="6" t="n">
-        <v>68</v>
+        <v>154</v>
       </c>
       <c r="I258" s="8" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="H259" s="6" t="n">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="I259" s="8" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         </is>
       </c>
       <c r="H260" s="6" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="I260" s="8" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="H261" s="6" t="n">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="I261" s="8" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         </is>
       </c>
       <c r="H262" s="6" t="n">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="I262" s="8" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="H263" s="6" t="n">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="I263" s="8" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="H264" s="6" t="n">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="I264" s="8" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="H265" s="6" t="n">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="I265" s="8" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="H266" s="6" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="I266" s="8" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="H267" s="6" t="n">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="I267" s="8" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         </is>
       </c>
       <c r="H268" s="6" t="n">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="I268" s="8" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="H269" s="6" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="I269" s="8" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         </is>
       </c>
       <c r="H270" s="6" t="n">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="I270" s="8" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         </is>
       </c>
       <c r="H271" s="6" t="n">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="I271" s="8" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="H272" s="6" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="I272" s="8" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         </is>
       </c>
       <c r="H273" s="6" t="n">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="I273" s="8" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="H274" s="6" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="I274" s="8" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="H275" s="6" t="n">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="I275" s="8" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         </is>
       </c>
       <c r="H276" s="6" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I276" s="8" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="H277" s="6" t="n">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="I277" s="8" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         </is>
       </c>
       <c r="H278" s="6" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="I278" s="8" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="H279" s="6" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="I279" s="8" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="H280" s="6" t="n">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="I280" s="8" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         </is>
       </c>
       <c r="H281" s="6" t="n">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="I281" s="8" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="H282" s="6" t="n">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="I282" s="8" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         </is>
       </c>
       <c r="H283" s="6" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="I283" s="8" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         </is>
       </c>
       <c r="H284" s="6" t="n">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="I284" s="8" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="H285" s="6" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I285" s="8" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         </is>
       </c>
       <c r="H286" s="6" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I286" s="8" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="H287" s="6" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I287" s="8" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="H288" s="6" t="n">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="I288" s="8" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         </is>
       </c>
       <c r="H289" s="6" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="I289" s="8" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="H290" s="6" t="n">
-        <v>176</v>
+        <v>104</v>
       </c>
       <c r="I290" s="8" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="H291" s="6" t="n">
-        <v>173</v>
+        <v>58</v>
       </c>
       <c r="I291" s="8" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         </is>
       </c>
       <c r="H292" s="6" t="n">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="I292" s="8" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         </is>
       </c>
       <c r="H293" s="6" t="n">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="I293" s="8" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="H294" s="6" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="I294" s="8" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         </is>
       </c>
       <c r="H295" s="6" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="I295" s="8" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         </is>
       </c>
       <c r="H296" s="6" t="n">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="I296" s="8" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="H297" s="6" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="I297" s="8" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="H298" s="6" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I298" s="8" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="H299" s="6" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I299" s="8" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="H300" s="6" t="n">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="I300" s="8" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="H301" s="6" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="I301" s="8" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>200</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>200</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>200</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>200</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>200</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>200</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>200</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>200</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>200</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>200</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>200</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>200</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>200</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>200</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>200</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>200</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>200</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>200</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>200</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>200</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>200</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>200</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>200</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>200</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>200</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>200</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>200</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>200</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>200</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>200</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>200</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>200</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>200</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>200</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>200</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>200</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>200</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>200</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>200</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>200</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>200</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>200</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>200</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>200</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>200</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>200</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>200</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>200</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>200</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>200</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>200</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>200</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>200</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>200</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>200</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>200</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>200</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>200</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>200</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>200</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>200</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>200</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>200</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>200</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>200</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>200</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>200</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>200</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>200</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>200</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>200</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>200</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>200</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>200</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>200</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>200</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>200</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>200</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>200</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>200</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>200</v>
       </c>
       <c r="G86" s="6" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>200</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>200</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>200</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>200</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>200</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>200</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>200</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>200</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>200</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>200</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>200</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>200</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>200</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>200</v>
       </c>
       <c r="G100" s="6" t="n">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>200</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>200</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>200</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>200</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>200</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>200</v>
       </c>
       <c r="G106" s="6" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>200</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>200</v>
       </c>
       <c r="G108" s="6" t="n">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>200</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>200</v>
       </c>
       <c r="G110" s="6" t="n">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>200</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>200</v>
       </c>
       <c r="G112" s="6" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>200</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>200</v>
       </c>
       <c r="G114" s="6" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>200</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>200</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>200</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>200</v>
       </c>
       <c r="G118" s="6" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>200</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>200</v>
       </c>
       <c r="G120" s="6" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>200</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>200</v>
       </c>
       <c r="G122" s="6" t="n">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>200</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>200</v>
       </c>
       <c r="G124" s="6" t="n">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>200</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>200</v>
       </c>
       <c r="G126" s="6" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>200</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>200</v>
       </c>
       <c r="G128" s="6" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>200</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>200</v>
       </c>
       <c r="G130" s="6" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>200</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>200</v>
       </c>
       <c r="G132" s="6" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>200</v>
       </c>
       <c r="G133" s="6" t="n">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>200</v>
       </c>
       <c r="G134" s="6" t="n">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>200</v>
       </c>
       <c r="G135" s="6" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>200</v>
       </c>
       <c r="G136" s="6" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>200</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>200</v>
       </c>
       <c r="G138" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>200</v>
       </c>
       <c r="G139" s="6" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>200</v>
       </c>
       <c r="G140" s="6" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>200</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>200</v>
       </c>
       <c r="G142" s="6" t="n">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>200</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>200</v>
       </c>
       <c r="G144" s="6" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>200</v>
       </c>
       <c r="G145" s="6" t="n">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>200</v>
       </c>
       <c r="G146" s="6" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>200</v>
       </c>
       <c r="G147" s="6" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H147" s="9" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>200</v>
       </c>
       <c r="G148" s="6" t="n">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>200</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>200</v>
       </c>
       <c r="G150" s="6" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>200</v>
       </c>
       <c r="G151" s="6" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>200</v>
       </c>
       <c r="G152" s="6" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>200</v>
       </c>
       <c r="G153" s="6" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>200</v>
       </c>
       <c r="G154" s="6" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>200</v>
       </c>
       <c r="G155" s="6" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>200</v>
       </c>
       <c r="G156" s="6" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>200</v>
       </c>
       <c r="G157" s="6" t="n">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>200</v>
       </c>
       <c r="G158" s="6" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>200</v>
       </c>
       <c r="G161" s="6" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>200</v>
       </c>
       <c r="G162" s="6" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H162" s="9" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>200</v>
       </c>
       <c r="G163" s="6" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>200</v>
       </c>
       <c r="G164" s="6" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>200</v>
       </c>
       <c r="G165" s="6" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>200</v>
       </c>
       <c r="G166" s="6" t="n">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>200</v>
       </c>
       <c r="G167" s="6" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H167" s="9" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>200</v>
       </c>
       <c r="G168" s="6" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H168" s="9" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>200</v>
       </c>
       <c r="G169" s="6" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>200</v>
       </c>
       <c r="G170" s="6" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H170" s="9" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>200</v>
       </c>
       <c r="G171" s="6" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>200</v>
       </c>
       <c r="G172" s="6" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="H172" s="9" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>200</v>
       </c>
       <c r="G173" s="6" t="n">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>200</v>
       </c>
       <c r="G174" s="6" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H174" s="9" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>200</v>
       </c>
       <c r="G175" s="6" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>200</v>
       </c>
       <c r="G176" s="6" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>200</v>
       </c>
       <c r="G177" s="6" t="n">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>200</v>
       </c>
       <c r="G178" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H178" s="9" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>200</v>
       </c>
       <c r="G179" s="6" t="n">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>200</v>
       </c>
       <c r="G180" s="6" t="n">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>200</v>
       </c>
       <c r="G181" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>200</v>
       </c>
       <c r="G182" s="6" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="H182" s="9" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>200</v>
       </c>
       <c r="G183" s="6" t="n">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>200</v>
       </c>
       <c r="G184" s="6" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="H184" s="9" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>200</v>
       </c>
       <c r="G185" s="6" t="n">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>200</v>
       </c>
       <c r="G186" s="6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H186" s="9" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>200</v>
       </c>
       <c r="G187" s="6" t="n">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>200</v>
       </c>
       <c r="G188" s="6" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="H188" s="9" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>200</v>
       </c>
       <c r="G189" s="6" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>200</v>
       </c>
       <c r="G190" s="6" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>200</v>
       </c>
       <c r="G191" s="6" t="n">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>200</v>
       </c>
       <c r="G192" s="6" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>200</v>
       </c>
       <c r="G193" s="6" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>200</v>
       </c>
       <c r="G194" s="6" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>200</v>
       </c>
       <c r="G195" s="6" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>200</v>
       </c>
       <c r="G196" s="6" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>200</v>
       </c>
       <c r="G197" s="6" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="G198" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>200</v>
       </c>
       <c r="G199" s="6" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>200</v>
       </c>
       <c r="G200" s="6" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>200</v>
       </c>
       <c r="G202" s="6" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>200</v>
       </c>
       <c r="G203" s="6" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>200</v>
       </c>
       <c r="G204" s="6" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>200</v>
       </c>
       <c r="G205" s="6" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>200</v>
       </c>
       <c r="G206" s="6" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>200</v>
       </c>
       <c r="G207" s="6" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>200</v>
       </c>
       <c r="G208" s="6" t="n">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="H208" s="9" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>200</v>
       </c>
       <c r="G209" s="6" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>200</v>
       </c>
       <c r="G210" s="6" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>200</v>
       </c>
       <c r="G211" s="6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>200</v>
       </c>
       <c r="G212" s="6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>200</v>
       </c>
       <c r="G213" s="6" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>200</v>
       </c>
       <c r="G214" s="6" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H214" s="9" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>200</v>
       </c>
       <c r="G215" s="6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>200</v>
       </c>
       <c r="G216" s="6" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H216" s="9" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>200</v>
       </c>
       <c r="G217" s="6" t="n">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="H217" s="9" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>200</v>
       </c>
       <c r="G218" s="6" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="H218" s="9" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>200</v>
       </c>
       <c r="G219" s="6" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>200</v>
       </c>
       <c r="G220" s="6" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H220" s="9" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>200</v>
       </c>
       <c r="G221" s="6" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>200</v>
       </c>
       <c r="G222" s="6" t="n">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="H222" s="9" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>200</v>
       </c>
       <c r="G223" s="6" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>200</v>
       </c>
       <c r="G224" s="6" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>200</v>
       </c>
       <c r="G225" s="6" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="H225" s="9" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>200</v>
       </c>
       <c r="G226" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>200</v>
       </c>
       <c r="G227" s="6" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="H227" s="9" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>200</v>
       </c>
       <c r="G228" s="6" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>200</v>
       </c>
       <c r="G229" s="6" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>200</v>
       </c>
       <c r="G231" s="6" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>200</v>
       </c>
       <c r="G232" s="6" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>200</v>
       </c>
       <c r="G233" s="6" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>200</v>
       </c>
       <c r="G234" s="6" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H234" s="9" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>200</v>
       </c>
       <c r="G235" s="6" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="H235" s="9" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>200</v>
       </c>
       <c r="G236" s="6" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H236" s="9" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>200</v>
       </c>
       <c r="G237" s="6" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H237" s="9" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>200</v>
       </c>
       <c r="G238" s="6" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H238" s="9" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>200</v>
       </c>
       <c r="G239" s="6" t="n">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>200</v>
       </c>
       <c r="G240" s="6" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>200</v>
       </c>
       <c r="G241" s="6" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="H241" s="9" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>200</v>
       </c>
       <c r="G242" s="6" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="H242" s="9" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>200</v>
       </c>
       <c r="G243" s="6" t="n">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="H243" s="9" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>200</v>
       </c>
       <c r="G244" s="6" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="H244" s="9" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>200</v>
       </c>
       <c r="G245" s="6" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H245" s="9" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>200</v>
       </c>
       <c r="G246" s="6" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H246" s="9" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>200</v>
       </c>
       <c r="G247" s="6" t="n">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="H247" s="9" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>200</v>
       </c>
       <c r="G248" s="6" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="H248" s="9" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>200</v>
       </c>
       <c r="G249" s="6" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="H249" s="9" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>200</v>
       </c>
       <c r="G250" s="6" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H250" s="9" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>200</v>
       </c>
       <c r="G251" s="6" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H251" s="9" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>200</v>
       </c>
       <c r="G252" s="6" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="H252" s="9" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>200</v>
       </c>
       <c r="G253" s="6" t="n">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="H253" s="9" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>200</v>
       </c>
       <c r="G254" s="6" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="H254" s="9" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>200</v>
       </c>
       <c r="G255" s="6" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="H255" s="9" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>200</v>
       </c>
       <c r="G256" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H256" s="9" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>200</v>
       </c>
       <c r="G257" s="6" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H257" s="9" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>200</v>
       </c>
       <c r="G258" s="6" t="n">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="H258" s="9" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>200</v>
       </c>
       <c r="G259" s="6" t="n">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="H259" s="9" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>200</v>
       </c>
       <c r="G260" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H260" s="9" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>200</v>
       </c>
       <c r="G261" s="6" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H261" s="9" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>200</v>
       </c>
       <c r="G262" s="6" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H262" s="9" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>200</v>
       </c>
       <c r="G263" s="6" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="H263" s="9" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>200</v>
       </c>
       <c r="G264" s="6" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>200</v>
       </c>
       <c r="G265" s="6" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>200</v>
       </c>
       <c r="G266" s="6" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>200</v>
       </c>
       <c r="G267" s="6" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>200</v>
       </c>
       <c r="G268" s="6" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>200</v>
       </c>
       <c r="G269" s="6" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>200</v>
       </c>
       <c r="G270" s="6" t="n">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>200</v>
       </c>
       <c r="G271" s="6" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="H271" s="9" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>200</v>
       </c>
       <c r="G272" s="6" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H272" s="9" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>200</v>
       </c>
       <c r="G273" s="6" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="H273" s="9" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>200</v>
       </c>
       <c r="G274" s="6" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H274" s="9" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>200</v>
       </c>
       <c r="G275" s="6" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H275" s="9" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>200</v>
       </c>
       <c r="G276" s="6" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="H276" s="9" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>200</v>
       </c>
       <c r="G277" s="6" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H277" s="9" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>200</v>
       </c>
       <c r="G278" s="6" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="H278" s="9" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>200</v>
       </c>
       <c r="G279" s="6" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="H279" s="9" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>200</v>
       </c>
       <c r="G280" s="6" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="H280" s="9" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>200</v>
       </c>
       <c r="G281" s="6" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H281" s="9" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>200</v>
       </c>
       <c r="G282" s="6" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="H282" s="9" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>200</v>
       </c>
       <c r="G283" s="6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H283" s="9" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>200</v>
       </c>
       <c r="G284" s="6" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H284" s="9" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>200</v>
       </c>
       <c r="G285" s="6" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H285" s="9" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>200</v>
       </c>
       <c r="G286" s="6" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H286" s="9" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>200</v>
       </c>
       <c r="G287" s="6" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H287" s="9" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>200</v>
       </c>
       <c r="G288" s="6" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="H288" s="9" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>200</v>
       </c>
       <c r="G289" s="6" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H289" s="9" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>200</v>
       </c>
       <c r="G290" s="6" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H290" s="9" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>200</v>
       </c>
       <c r="G291" s="6" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H291" s="9" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>200</v>
       </c>
       <c r="G292" s="6" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="H292" s="9" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>200</v>
       </c>
       <c r="G293" s="6" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H293" s="9" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>200</v>
       </c>
       <c r="G294" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H294" s="9" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>200</v>
       </c>
       <c r="G295" s="6" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="H295" s="9" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>200</v>
       </c>
       <c r="G296" s="6" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H296" s="9" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>200</v>
       </c>
       <c r="G297" s="6" t="n">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="H297" s="9" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>200</v>
       </c>
       <c r="G298" s="6" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="H298" s="9" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>200</v>
       </c>
       <c r="G299" s="6" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H299" s="9" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>200</v>
       </c>
       <c r="G300" s="6" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H300" s="9" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>200</v>
       </c>
       <c r="G301" s="6" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H301" s="9" t="inlineStr">
         <is>
